--- a/schedule/data/daily_quotes.xlsx
+++ b/schedule/data/daily_quotes.xlsx
@@ -1,108 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gyt_system\zhiban_cloud_system\schedule\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F72FBE-CEC6-406E-A96D-B5D469A1D8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_quotes" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_quotes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">daily_quotes!$A$1:$D$8</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>content</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>active</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发心护持道场，就是培福培慧。</t>
-  </si>
-  <si>
-    <t>欢喜做事，福慧增长。</t>
-  </si>
-  <si>
-    <t>一切善法，皆从恭敬中来。</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -110,50 +50,89 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -441,91 +420,2386 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D144"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>感恩觀世音菩薩
+禪妙一曲觀世音,
+救苦救難是心經。
+大慈大悲菩提心,
+出離苦海傳妙音。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>每天要活在感恩中,感恩是蓮花,
+在蓮花中成長, 你一定會法喜充滿。
+貪心會增加壓力,
+守戒能減輕恐懼,
+紅塵會增加瞋恨,
+學佛能改變六根。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>傳統文化有一句話,
+吃虧就是便宜,
+實際上是很有哲理。
+吃虧,其實就是消業,
+消業後你就會有轉機。
+有轉機,就代表著進步。
+所以當你進步的時候,
+你已經遠離那些痛苦和煩惱。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>心靈的光芒,
+包含著“知行智慧”之光。
+擁有知行智慧之光,
+再去踐行佛道,
+你就擁有了“知行合一”
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>學佛再多,不能擺脫痛苦,
+這就叫理論在實踐中的迷惑。
+學佛後,擺脫了痛苦,
+解脫了煩惱,放下了執著,
+那你才是真正的
+讓佛性之光在你心中閃亮。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>佛性是覺悟之身,
+又是般若智慧,
+只有佛性,
+才能產生“自淨其意”,
+才能克服煩惱。
+瞬間的想不通,
+只要引用正確的佛的思維,
+踐行佛道,就能解脫。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>靈魂之處戒貪欲,
+心靈深處得解脫。
+在人間凡是看得見的,
+都能解決;
+看不見的,被污染都不知道,
+那就是你的靈魂。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>“白话佛法”
+能幫助你擦拭
+內心八識田中的污垢。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>脫離六道,必須隨緣。 紅塵中攀緣,跳不出五行, 離不開三界,脫不了六道。
+內心不煩,外心不貪。
+内心、外心, 均是“無所謂”,
+佛法界講是“無所得”。
+“無所得”,就是“無罣礙”
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>狂妄的人是因為他沒有狂妄過;
+高傲自大的人是過去沒有高傲過;
+愚癡的人是他不知道自己愚癡。
+只有知道什麼叫狂妄, 自己才不會去狂妄;
+只有知道什麼叫高傲, 自己才不會去高傲;
+只有知道什麼叫愚癡, 自己才不會去愚癡;
+只有知道什麼叫業障, 自己才不會去造業。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>學佛遇煩惱,
+這是增長智慧的好機會。
+學佛遇障礙,
+這是心靈開悟的增上緣。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>能夠理解別人,那就叫莊嚴。
+有福之人,是因為他的忍耐。
+勤修莫過於寡欲,寡欲才能知足。
+知足之人,雖貧而富; 不知足之人,雖富而貧。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>整天盯著別人缺點的人,
+你會失去自己的安詳心態 和你在別人心中的莊嚴之相。
+因為你不傷害別人,
+別人才會尊重你的正直。
+我們學佛人,要請佛住心,
+心中才能清淨無染。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>一個人不懂“路”,才會走“錯路”;
+一個人不懂“道”,才會不“知道”。
+知道這條“道”
+才不會走錯這條“道”:
+知道佛這條“道”
+你才能找到“佛道”
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>用心去做好每一件事情。
+緣來了,多發心;
+緣結束,就收心。
+能夠理解事物的本性是空性,
+你就會瞭解什麼叫菩提心。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>人的一生,
+必須完成圓滿自性和瞭解本性。
+“自性”和“本性”
+就是讓你要知道事物的真相。
+能夠理解事物和緣分的結局,
+能夠瞭解人跟人的緣分結果, 這個過程就是“由無常到空性”。
+所以緣分只是一種銜接和回憶, 它是如夢幻泡影,如露亦如電。
+學會隨緣觀,就是如是觀。
+緣生緣滅,如如不動。 起心動念,觀性即空。
+所生喜心,只是緣起。 所生苦心,只是性空。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>幻覺來時假亦真, 虛幻紅塵真亦假。
+緣來緣去人間夢, 借假修真夢成真。
+覺醒是佛, 修心是道。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>誠實是學佛的資本,
+勤奮是學佛的基礎,
+善良是學佛的根基, 慈悲是學佛的源泉。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>總是為別人想,
+你的想蘊將越來越純潔。
+整天為自己想,
+你的識蘊會越來越染垢。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>為別人而法喜,那是廣發菩提心;
+為別人而悲傷,那是悲愍眾生心;
+喜歡嘲笑別人,那是因為你的劣根;
+喜歡跟人攀比,那是累世所種因緣。
+願意幫助別人,那是因為你的善種;
+願意慈悲別人,那是因為你的佛性。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>萬法唯心所造,
+財富唯心所現。
+放下對身外之物的執著,
+才能破除偏執,消除我見。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>不為自身求安樂,願與眾生共離苦。
+無欲無求勤修行,心中極樂善相應。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>貪愛富貴是貧窮之因,
+勤儉艱苦是富貴之果。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>當你心在如如不動的時候, 外境和外塵的虛幻
+就會在你的心中慢慢過去。
+嫉妒像一把火, 只要這一把火燃著了,
+就會燒到別人和自己。
+嫉妒心是人類的一大障礙。
+擁有嫉妒,失去慈悲。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>能為別人做事, 要視作自己的福德。
+當一個人不能夠幫助別人的時候,
+說明你已經失去了幫助別人的能力和力量。
+所以盡自己的力量去幫助別人,
+哪怕語言布施,都是善德的累積。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>人其實最要解決的就是因果病。
+因果會讓你失去心靈上的快樂;
+因果會讓你付出憂鬱和恐懼的代價。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>因果病的最好良藥,是慈悲喜捨。
+種下慈悲因,沒有憂鬱果;
+種下喜捨因,沒有恐懼果。
+捨去一點恨,得到多點愛;
+捨去一點自私,得到多點歡喜。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>常生歡喜心,捨去瞋恨心;
+常生慈悲心,捨去嫉妒心;
+清淨心能消業障,慈悲心能保平安。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>信解行證, 首先靠得是信心。
+學佛人的境界, 是和你恭敬虔誠的內心一起生長。
+以凡人之心,做菩薩之事, 必定遠離定慧。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>降伏貪心,靠的是戒律;
+降伏癡心,靠的是智慧;
+降伏妄心,靠的是定力。
+修心要斷惡修善, 行善積德,眾善奉行。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>一個人的一生,
+就如同你的身體一樣,
+到處都會出問題,
+到處都需要調節。
+沒有攀登不了的高峰,
+只有缺少信心的凡人。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>紅塵滾滾不可貪,
+欲海沉淪不可得。
+虛幻顛倒夢一場,
+學佛離幻志如鋼。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>“私欲”
+是人的一種自憐自愛的產物,
+它只會讓你變得越來越可憐。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>心態要常保持正念。
+心態就是你心裡對
+某個人或一件事情的態度,
+這個態度來自於你的六根。
+乾淨的六根,會有一個好的心態;
+污濁的六根,
+會使你在人間變得非常的苦惱。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>擁有一個坦蕩清淨、純潔的心態,
+你的心態一定會變得光明磊落。
+擁有一個不爭不貪的心態,
+你的心將會處之坦然。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>煩惱在心中化不掉,
+時間長了,它就是一顆沙子,
+經常會磨損你的心臟,讓你“心痛”。
+學佛人要學會融化自己的煩惱,
+就像白雲經常融化在藍天之中。
+心情不好, 要學會換環境,學會轉移思維。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>學會聽《白話佛法》, 把思想集中來聽,
+你的雜念馬上會去除。 剛剛有很痛苦的雜念,
+馬上打開《白話佛法》來聽, 而且跟著師父所講的內容,
+你很快就遠離了煩惱, 清淨了頭腦,靈得不得了。
+心會慢慢定下來,智慧慢慢生出來。
+師父都是這樣, 當師父有煩惱的時候,
+師父就全身心地聽, 馬上把其他的雜念全部漏光。
+所以正思惟, 就是漏盡雜念,漏光煩惱。
+(有太多人使用了這個方法之後, 離念轉境。)
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>菩薩說,學佛重在“践行”,
+實實在在地去學佛,去做功德,
+你就會有無漏的功德。
+人精神上正念一漏,就會亂想。
+越亂想,越要想, 最後邪思邪念全來了。
+經常失去正念的人, 會影響身體健康。
+所以凡是胡思亂想、思想不集中的人,就叫“神漏”。
+充滿智慧的人生,必須有無漏智慧。
+虛幻世界離相修, 知足常樂菩薩救。
+遠離紅塵境界高, 禪定妙心離六道。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>少說少是非，多說多是非，不說無是非。
+少看少煩惱，多看多煩惱，不看沒煩惱。
+少想不種因，多想神經病，不想腦子輕。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>“欲望”來自於我們的無明。
+“苦行”能斷除因欲望而產生的煩惱。
+“願力”是你信心的源泉。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>廣發無上菩提心，度盡眾生大願心，
+有業所障無明心，緣起性空修佛心。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>一個人要學會“相應”。
+“相應”就是你能做什麼，你才能夠去做什麼；
+你應該想什麼，你才能想什麼；
+你可以說什麼，你才應該說什麼。
+如果不相應，做了不該做的，說了不該說的，想了不該想的，
+你就是“妄動、妄語、妄想”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>正信正念正能量，信佛修心志如鋼，
+轉識成智消業障，智慧如海在慈航。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>活在“貪瞋癡”當中，你永遠得不到真正的快樂。
+幸福和痛苦，只是你的一種感覺，而這種感覺有時瞬間變化。
+幸福來得快，去得也快；痛苦也是如此。
+年輕時我們有多少這種幸福和痛苦的感覺，現在都找不到了。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>“雜念”會讓你把“自性”的光芒遮蓋。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>學佛要“性命雙修”。
+“性”指人的心性、思維、品性、性情。
+“命”指人的身體、生命能量、命運和物質。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>性命雙修，就是精神和人身同時修，
+才能福慧雙收，延年益壽。
+修心不修命，以後必生病。
+修命不修性，精神會有病。
+“吾善養吾浩然正氣，浩浩乎塞乎天地之間。”
+所以學佛修心，福慧雙修，性命雙修，
+讓你的本性更加純潔。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>有時候坐在觀音堂，每個人都在想，
+人身難得，猶如“盲龜值木”。
+學會珍惜人生，借假修真，身心兩全，超凡入聖，才能見證佛性。
+經常想想，用你在求佛時的這種心情，去慈悲一切有緣眾生，廣結善緣，行善積德，這樣你的功德與發心，才會功德圓滿。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>身作菩提心，心發菩提願，
+常念慈悲心，住心大悲願。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>修心不在於形式，而是要看你的“心”。
+常能深沉地懺悔，佛性常存“深般若”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>修行就是修心，修到後來，
+心和行為越來越有悟性，
+進入深層般若，
+這就是“行深般若”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>學佛人要知道，把自己的“心門”打開，佛光才能照到你的心裡。
+天天心裡在想一些不能告訴別人的事情，就會有不好的邪念來纏你。
+所以，真正會修心的人，就把自己當成菩薩，就把自己的“心念”當成“佛念”，
+這就叫“即心即佛”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>學佛人靠“心智”生活，
+不學佛人靠“因果”生活，
+凡夫俗子跟著“業障”生活。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>師父曾和你們說過，身體是你的客人，心是你的主人。
+身體這個客人，想來就來，不想來就走；
+心才是你的主人，任何時候，你都和心在一起。
+當你修出人道了，你就會擁有“菩薩心”；能修到天上成佛，你就是擁有“佛心”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>菩薩說過，“至高無上的佛，就是自己的心”。
+你的心可以管住你的一切，所以“起心動念”無不是業。
+正道正道走佛道，墮落墮落邪迷竅，
+慧命慧命開悟心，學佛慧命天上行。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>任何一個對自己行為不負責任的人，就是對別人不負責。
+愛護好自己就是愛護眾生。
+人生煩惱剪不斷，懶得做事也要幹。
+放下貪欲求平安，五欲六塵冷眼看，解脫煩惱求平安。
+只有放下才能解脫。什麼叫解脫？想通了就是“解脫”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>什麼叫放下？不去想了，就叫“放下”。
+人有智慧，就會產生莊嚴，大家會尊重你，
+所以智慧比任何你擁有的物質更重要。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>師父曾經跟大家說過，要自主煩惱，
+就是自己能控制自己的煩惱。
+沒有智慧，你會被煩惱所控制；
+有了智慧，你才能控制煩惱。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>什麼叫“神通”？“神”就是精神，“通”就是想通。
+一個人精神上想通，他就有神通；
+能夠脫離煩惱的人，他就是有“神通”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>放下了名利，脫離了煩惱。
+遠離了無明，擁有了般若。
+一定要用正能量，來戰勝自己內心的私欲，
+你就會擁有“四無量心”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>遠離嫉恨修清淨，離苦得樂出離心。
+雜念業障消乾淨，念佛常懷慈悲心。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>如如不動，佛在心中。有心即苦，無心即樂。
+在人間要學會“承受”，因為人間“不圓滿”，
+所以懂得“承受”本身就是一種“消業”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>在人間就已經能擁有精神的快樂，說明你清淨無染，
+遠離煩惱，你已經生活在人間聖境。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>不貪不求的人生，已經是覺悟的智者，
+說明你已經擁有了出離心。
+“出離心”越強，“貪愛心”就越弱；
+“貪愛心”越強，出離的“道心”就越弱。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>福慧雙修是智者，悲智雙運是悟者，
+入世修行是聖者，出世之心是覺者。
+師父告訴你們，“過去何必思量，
+現在不用緊張，念佛自然吉祥”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>人若修心想長壽，心胸寬廣莫要愁。
+不貪不淫走正道，眾善奉行境界高。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>想成佛的人，實際上他的心，
+已經像佛了，因為一切唯心造。
+當你在行善時，你的心跟佛是一如的；
+當你在行惡時，你的心和魔是一如的。
+一個善良的人，做出來的一定是善事；
+一個邪惡的人，想出來的一定是邪念。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>當你一天沒有念經，你會感覺到魂魄不全、神志不清。
+當你一碰到事情就念經，你是一個頭腦清晰、神清氣爽之人。
+因為正信正念的意識，指導了你的所作所為。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>如果心中無佛，你一定不知做的是好事壞事，
+說明你的心離佛太遠；如果你做每一件事情，
+都想著要跟佛菩薩一樣，說明你“佛性常住”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>“心性”要一如，“心”就是你的意識，“性”就是你的佛性。
+“心性一如”，你就可以如如不動。
+一邊修心，一邊改念。要用正確的理念和崇高的境界，
+約束自己的語言和行為。常看自己內心的“佛性”，
+常觀自己的“法身”，你內心的佛光就會普照，
+佛性長存，你就會擁有慧命和生命。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>身體只是你的陰陽五行假合之身。
+只有心靈不受苦，你的肉身才會不受苦；
+只有健康的心靈，才會擁有健康的身體。
+如夢如幻如泡影，如露如電如是觀，
+苦空無常是真諦，修出六道佛真意。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>知佛心者懂人心。理解自己的脾氣，
+能讓自己更好地和別人相處。
+理解眾生苦難，能讓自己的心得到更多安寧。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>佛讓我們“捨去放下”，就是不要心中有“是非”。
+連“非”都不要，何況有“是”。因為“是”就是你認為某一件事情你“是”對的，
+你就會認為別人不對。
+“非”就是因為你認為別人是“錯的”，你就會心中覺得你是“對的”。
+其實這已經違背了佛法的“因果規律”。
+要經常想，沒有因果，我會碰上他嗎？沒有因緣，我會生氣嗎？
+沒有因果，我會有今天這樣的煩惱嗎？
+一切都是緣分，善惡因緣都要受，這樣你才能對治自己的“瞋恚”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>恨別人時，要想到別人可憐的地方。
+當你用“慈悲心”去思考心中煩惱時，
+你就會沒有“恨念”，你只會感覺到他很“可憐”。
+請記住師父跟你們說的這句話：當你恨別人的時候，
+別人不一定知道，而你自己會恨得很難受。
+最終受傷害的，一定是你自己。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>學會“奉獻”，才能接受“忍辱”；不願意奉獻的人，
+不會“忍辱”。想想今天恨，明天愛，過去愛，現在恨；
+想想世界沒有一件事情是永恆不變的。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>如果你經常能想到守戒，不爭不吵，
+守戒寂靜，你就獲得了別人尊重你的基礎。
+想要別人尊重你，要學會守戒律，規範自己的道德品質。
+1. 平常不亂說話。2. 戒“殺盜淫妄酒”。
+3. 為人有恆心和毅力。4. 學會幫助別人，需要有恆心。
+5. 放下人間是非事，一心只念觀世音。
+學會保持禪定狀態，雜念就會離你而去。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>禪智禪修能禪定，念經無心不安靜。
+心智穩定禪定行，念離痛苦禪道心。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>人情是紙張張薄，學佛暖心娑婆訶。
+佛智佛念願力強，法喜充滿像太陽。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>學佛彌勒度量大，哈哈一笑人太傻。
+你不生氣哪來氣，想通放下解真諦。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>放下煩惱哈哈笑，貪圖名利哇哇叫，
+慈悲喜捨呱呱叫，學佛修心是良藥。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>有智慧的人，會用別人的智慧去解決問題；
+沒智慧的人，會以為自己很有智慧地去解決問題，結果越搞越糟。
+用大悲心去解決一切煩惱，這就是“無礙大悲心陀羅尼”。
+白話佛法說：把每件事情做得好，做到底，就是功德圓滿。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>念禮佛大懺悔文注重點：
+1.整個禮佛大懺悔文，必須認真無漏。
+2.稱佛號要莊嚴尊敬。
+3.當念到“我昔所造諸惡業，皆由無始貪瞋癡。從身語意之所生，一切我今皆懺悔”這四句要特別用懺悔心來念。
+4.“所有眾生身口意，見惑彈謗我法等。 如是一切諸業障，悉皆消滅盡無餘。”
+要以極其真誠的心來念。（這樣念經效果會更好。師父開示。）
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>現實生活中如果你有“怨恨”，因為怨和恨是相續的，
+怨了就會恨，越怨越會恨，恨了就會遮蓋慈悲清淨的本性，
+在佛法界說叫“瞋恚”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>不能讓自己醒悟的心在情緒低落中昏沉。
+就猶如一個睡不醒的人，不管讓他再睡多少時間，他也會貪睡。
+假裝睡覺的人是叫不醒的；不想學佛的人是度不了的。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>“心性”有分陰陽，心性過多地去接觸陰氣的人，會做惡夢，會沒有精氣神，會提不起正念。在佛法界稱為“陰身”。
+所以有時候我們在一個人身邊，突然感覺心一陣疲憊，昏昏欲睡，
+實際上你已經受到“陰身”的傷害，會迷失精氣神。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>陰身之人，沉默寡歡，常痛苦，常難過，妄念紛飛，情緒會不穩。
+要改變“陰身”，必須堅定信心，常想菩薩保佑我，常念“過去不可得”，
+持之以恆，修持佛法；情緒不好時，想到一切都會過去。
+用善法改變自我。一碰到情緒不好，馬上念大悲咒7遍、心經7遍、
+消災吉祥神咒7遍，會讓你心情好起來，遠離痛苦煩惱。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>學佛人要去除多疑症。
+多疑之人，會加深自己的心病，阻礙自己的修心。
+紅塵滾滾無取捨，空中樓閣盡虛空。
+心包太虛無四相，菩提境界遍法界。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>菩薩總是給我們很多機會，讓我們來改掉自身的毛病。
+一個人的脾氣越倔，說明紅塵的根性越重。因為脾氣代表著你的某一種思維。思維想不通，就會有脾氣。思維想得通，整天笑嘻嘻。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>“脾氣”是因為你心中有是非。經常有對錯，會產生我執，從而產生我慢。“我永遠是對的”，你就會生氣，就會放不下。
+看破放下是智慧，糾結執著沒富貴。禪智無礙易解脫，放下執著去托缽。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>學佛要將凡心入佛心，認識世界上一切“苦空無常”。能夠想到這個世界還很苦，能夠感受這個世界最後是空的，能夠理解這個世界一切都是會變的，是無常的，你就擁有了佛法的真諦“苦空無常”。
+是心作佛，是心是佛，佛就是心，心就是佛。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>當一個人內心有道德，有品德，有菩薩，有慈悲，你就是人間菩薩。
+無憂無慮多開心，何處沒有佛友情。慈悲喜捨忘私情，擦亮佛心見本性。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>觀世音菩薩讓我們要擁有解決人間煩惱的方法，其實這種方法就稱為“法力”。法力無邊，就是因為我們擁有了超人的智慧。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>一個人的“智慧”能得到莊嚴，是因為你比別人有智慧，別人就會尊重你；因為你擁有良好的意念，別人都會愛戴你；因為你有道德和福氣，所以你就擁有了“福德”。
+宜將善良變慈悲，不可貢高我慢歸。因緣果報人間累，佛性佛情本性回。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>常觀心無常，你就會遠離五濁惡世。常觀心無邪，你就會遠離六道輪迴。
+“戒定慧”是救度眾生的開始。你守戒，你就能夠救人；你定得下來，你就能夠修成佛；你有智慧，你就會擁有超出人間一切煩惱的“法力”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>記住，常恨別人，心裡會恨出魔性。常善良，常慈悲，你的本性常存九識田中。
+意念造就了你的因果，意識決定了你的本性。
+一心禪定修心淨，一念慈悲菩薩應，一種因緣用善心，一生修心成佛因。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>當有人關心你和幫助你，你就是一個很幸褔的人。當有佛友相互問候時，你應該覺得法喜充滿。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>世界因為疫情，生活的空間變得越來越狹窄。學佛人，要懂得這是“無常”的變化，明白一切都是正常的。要學會能夠適應它，然後學會改變自己的生活環境，去適應現在的生活，你才能駕馭生活。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>環境對學佛人的影響很大，這叫“對境起意”“住色生心”。一種利益，會讓你忘記佛性。一種外境，會讓你丟失般若。所以學佛要“無所住心”，才是真實不虛。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>人的心，會產生各種意念，但“妄念”會相續不斷，會讓你變得“癡心妄想”“迷惑顛倒”。所以永遠不要把人間的一個妄境、妄念，成為自己內心剪不斷、理還亂的“妄心”，讓自己生活在“迷惑顛倒”中。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>心不要隨便亂動，一動就停不下來。就猶如火車一樣，火車啟動後，它停不下來。別人的一句話、一個眼神，讓你心念一動，它會長久地住心，停不下來地不斷傷害自己。這就是為何菩薩要我們“無所住心”的道理。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>“不應住色生心，不應住聲香味觸法生心。”如果你把人間的一切境界、煩惱看破放下，你就等於生出了“清淨心”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>“應無所住而生其心。”舉個例子，別人說你不好，你沒放在心中，你就是沒把別人的這句話住在你的心中而生出其他的雜念來。這樣，你才能像佛一樣，修出“不生不滅的空性”，而且你很快就忘了別人的惡念，繼續和別人慈悲地交往。這在佛經上稱為“包容萬象，生出萬法”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>心無所動是智慧，心無所住本性歸。看破離開執著心，無所住心生其心。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>苦難由“心念”聚集而成。心是明鏡台，勿使惹塵埃。人間的種種執著、欲望、煩惱，只有當你遠離，才能捨去對“有”和“空”的執著。所以學佛，既要“不住心”，又不能執著於“無住”。經常想一下，一切的一切均是夢幻泡影，有何芥蒂分別可以常住在心。
+拋開名相分別，遠離妄心一切。煩惱不再糾結，無所住心空也。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>人要珍惜緣分。善緣來了，延續的時間很短，如果你把它保持住，善緣就可以延續。惡緣來了，千萬不能加重它的惡果，它會提早爆發；學會忍耐，惡果就不會馬上爆發。佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>佛經上說，“因緣會遇時，果報還自受”。
+其實善惡都是果報，不必去追究誰是誰非。
+善緣來了需延續，惡緣來了忍耐聚。因果報應隨時候，果報到時還自受。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>殺生的果報很大。師父告訴你們，殺生會斷了你的大悲種；並且當你有善緣來的時候，那些業障不會讓你得到善報，會讓你的善緣全部漏光。
+因殺業產生的業障，會在前世、今生、來世三世都會有報應，所以千萬要斷除“殺業根”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>莫權衡利弊得失，你就會遠離災禍。每天算計動私心，你會失去慈悲心。
+因緣不成求不到，因緣成熟佛知道。煩惱痛苦未修好，誠心懺悔善早報。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>寫“心得”是一種福德的布施。“心得”寫出來，龍天護法功德無量。弘法出去法布施，佛友看了後，增加佛友的正能量，因此你也有功德。其實這是法布施的一種“大功德”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>斷除煩惱才能解脫。在人間很多時候，想想自己很苦，但是你想一下有些人不知道比你還要苦多少倍，他們沒有聞到佛法，這樣你會生出慈悲心，你會放下自己的煩惱，這也是被稱作為“自我解脫”的一種。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>人間的對錯，只是你對自己有沒有好處的一種考量。所以不要讓別人對你的無私奉獻來成全你的自私。
+很多人有利益的事情就做，沒利益的事情不做，每天活在自我欺騙的人格當中。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>雜念專門跟你搞，看你境界高不高。
+修得乾淨自己好，修不乾淨增煩惱。
+人不能總是“找理由”，“找理由”就是執著的一種。執著了就會生出業障。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>今生能聞到佛法就是你的福氣，這是進入了聲聞道。緣來了，要覺悟，你才能找到佛道，這就叫緣覺道。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>煩惱來了一定有辦法根治。有個人，打苦工打了二十年，最後被人家開除了，他很難過，很痛心， 但是就在這時候，他聞到了佛法，他知道舊的不去，新的不來，結果三個月不到，他找到了工作，比原來工作不知好多少倍，工資也比原來的高。他逢人就說，這就是聞法後的福氣。其實這就是進入人間“聲聞道”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>煩惱即菩提。你如果沒有煩惱，你想不到要去求佛、拜佛、學佛。
+要牢記師父那句話：“過去何必思量，現在不必緊張，念佛自然安詳。”
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>菩薩在心中，煩惱一切空。
+心中經常想，觀世音菩薩聞聲救苦，我是善人在學佛，菩薩一定會救我。我要用慈悲心行佛道，看破放下境界高。你就會進入“色即是空，空即是色”的境界。
+只要你心中有個清淨的道場，菩薩一定會常住在你心中。
+心中常有清淨田，菩薩到來只瞬間。色即空來煩惱淹，空即色來只等閒。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>學佛人“淨信”很重要，你求菩薩你要完全的相信，這就叫“淨信”。
+“淨信”是你在鑄造心裡的“福田”。“淨信”讓你生起正能量的“勇氣”。
+徹底相信因果，你將會擁有三福田。徹底地淨信佛緣，你將會得到善果福報。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>福田供養福氣生，恩田孝順懂感恩，悲田慈悲有佛根，一生福慧遠離恨。
+學佛中有些人求了有福，有些人求了還沒福，其實就是你福報的種子種下去的早晚，所以結果有早晚。早種早得“福”，晚種晚得“福”，不種不得“福”。
+就像一個人排隊買東西一樣，排得早，買得到；排得晚，晚買到。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>早點想通，身體就好，“心臟”也快樂。晚點想通，脾臟和肝臟都會受損傷。
+聽了別人的惡話，就氣得半死，說明你被陰風一吹就倒，心中沒有防火牆。被別人一罵，就氣得不得了，說明你文化程度還不高，心中沒有正能量。被人家一說，就不學佛了，說明你沒有淨信心，信佛信得不乾淨、不徹底。
+自在安詳能化緣，善惡因緣不結冤。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>躲過疫情豔陽天，佛情佛意在心間。
+要完全相信觀世音菩薩，沒有半點懷疑心。
+抬頭吾佛觀世音，心中藏滿慈悲心。救苦救難傳法音，一生跟隨觀世音。
+淨信會讓你增加智慧，會讓你避開一切煩惱，福和慧自然到。淨信的人會把心安住，心不妄動，方可修出自性。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>看一看修得好的人，哪一個學佛沒有淨信心。
+現在的天時要學會：隨順因緣，平安是福。現在的天災要學會：無怨無恨，知足常樂。
+理解現實，你才能安排生活。理解人間，你才能救度人心。
+學佛拜佛自在佛，人間淨土長住佛，隨順眾生隨緣佛，法界藏身彌陀佛。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>學佛要管控好自己的心。心不亂動，人像青松；心一貪動，業障開工。
+一切都是緣分。“緣聚緣散”都是一種現象。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>學佛人要學會激活心中的“正能量”。念經後，只要有了感恩心，就是“正能量”。拜佛後，煩惱事放下了，就是“正能量”。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>把學佛心得告訴別人，讓別人法喜充滿，就是“正能量”。
+把菩薩拜到自己的心裡，每天看到菩薩，就是“正能量”。學佛人在生活中要注意一件事，就是心勿貪多。貪了就痛苦了，貪多沒好事。佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>吃得多，腸胃不好。想多了，腦子不好。身體累多了，健康不好。抽菸多了，免疫系統不好。喝酒多了，肝臟系統不好。錢多了，多花錢和被騙機會多了。享樂多了，作孽多了。生氣多了，煩惱多了。
+什麼事情都要適中，所以佛法說“中庸之道”。
+昨天跟你們說淨信，今天跟你們說不要迷信。迷信會讓你忘記你自己的智慧德能。
+貪心太多失自性，迷信太多丟本性，捨棄貪求有淨信，超凡入聖修空性。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>人生的真諦，你只要“從色看到空”，你就能看到“空即是色”也。
+接受現在，善果可摘。糾結現在，煩惱不該。學佛自在，放下短暫。想通自在，聽佛安排。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>學佛人一定要明白，煩惱是一輩子的事。一個煩惱結束了，另一個煩惱又來了。所以菩薩說，煩惱也是“業報輪迴”。
+既然一生有煩不完的事，就一定要用般若智慧去解決它。少看少煩惱，少聽少煩惱，少想少煩惱。人生短暫，唯有珍惜當下。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>因為人的思維，有太多的貪欲，貪欲會控制你的心，所以只要心一煩，惱怒就來了，所以叫“煩惱”。
+師父要培養你們積福積德。多為別人想，不消福，就會少業障，就沒煩惱，煩惱會隨著業障的減少而消失。經常學會想，“我夠了”“我有了”“我飽了”“感恩你”，人就不會貪，也不會爭。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>不貪不爭乘慈航，煩惱輪迴找不上，積福積德志如剛，誰不貪心誰最強。
+“煩惱”是你的心態造成的，學會平衡自己的心態。得到時，想到“我夠了”；失去時，想到“我過去已經有過，現在很滿足了”。
+一種理念常想到，得到的會失去，不要爭。一種思維常想到，煩惱是一種幻覺，最後空空如也。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>要常感到知足。別人擁有的東西，並不是你一定需要的；你擁有的東西，別人也不一定有。
+學佛中要“視有相無相為空相”。今天有，明天沒有；今天得到，明天失去，到最後一場空。所以“凡所有相皆屬虛妄”。佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>師父讓你們一輩子不要去跟別人爭鬥。想平安，要學會“謙讓”“迴避”和“化解”。別人有，恭喜他；自己有，分給他。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>人的一生辛苦賺錢，但最後帶不走一分錢。人的一生不顧身體拼命賺錢，最後錢可以把你的命帶走。
+普渡眾生了凡塵，知足常樂慈悲根。沒有嫉妒沒有恨，平安吉祥過一生。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>生活煩惱不厭倦，磕頭念經許大願。命運不好不埋怨，求佛禮懺福壽全。
+當一個人在受果報的時候，實際上就是他的因果成熟和因緣聚合了。這個果報不在乎於善和惡。因為眾生在時空的流轉中，輪迴了身體，無法知道前世自己種下的善和惡。待承受果報時，有的人在得意忘形中，命運突轉，然後怨天怨地；
+有的人在痛苦絕望時，突然像中彩票一樣，幸運降到了他的身上。學佛之後才明白，這只是善惡果報成熟的一種表現。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>哪有你一輩子的福可以享。哪有你一輩子的苦可以受。因緣會聚時，果報還自受。
+果報到了，又稱“自作自受”。因為“自作”是在上輩子，“自受”是在這輩子。
+有的人行善是在上輩子，享受福報是在這輩子。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>學佛就可以轉化定業。《了凡四訓》就是這樣的，一個本來應該受苦的人，卻能通過學佛轉變命運，福智雙全。
+學佛就是懂因果。懂得因，不種因，哪來果？懂得果，不碰因，何來果？
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>擁有正確的人生觀，掌握好命運的舵，船到橋頭自然直。轉換境界，適應環境，自度度他，不管在什麼情況下，你都能把握住佛法真諦。這個真諦就是，因果成熟終有報。這個真諦就是，因果從來不誤人。這個真諦就是，學佛改命又改運。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>敬畏因果少輪迴，放下瞋恨慈心歸。化解冤結沒業追，知因解脫無所謂，一生行善有福慧。
+因果一旦成熟，誰也無法阻止。就像一個人，每天抽點菸，幾十年下來，他的肺終有一天會壞。師父讓你們不要去觸動惡緣和緣種。緣分的種子得不到養料，就會枯萎。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>不管善惡緣，雖然緣分未盡，你不去碰緣分，它就不會產生後果。所以轉定業就是這麼轉換的。倒楣了，過去為什麼講“過一過二不過三”，因為報應是相續的。如果能在第一個果報現前時，馬上念經、修心、行善，雖然善惡不能抵消，但是善惡能“互相影響”。惡緣的晚成熟或是“重業輕報”，都是你“轉化定業”的方法。
+行善終有福，作惡冤有主。懺悔仇作古，放下不在乎。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>人的一生離不開“懺悔”。無始劫以來，我們做錯了太多，所以只有在內心真正地懺悔，才能消掉自己內心的業障和愧疚感。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>人的一生很多錯誤，是自己在不知道是錯誤的情況下做錯的，但它畢竟是錯的。罪業雖無自性，但因果有報應。
+惡念惡行不管大小，都會在你的八識田中，污染你的善良本性。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>念禮佛大懺悔文，就是請菩薩給你加持，來消除你過去所作的孽力，讓業力的種子不再生長出孽障。
+修養越高、境界越高的人，越能和別人說“對不起，我錯了”，其實這就是人間的實心懺悔。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>因為過去對別人的傷害，可能無法消除別人心中的芥蒂，只有靠真心懺悔，對方能感受到你的懺悔的力量；你自己也能通過懺悔，內心取得平安和心理健康。
+所以念禮佛大懺悔文，是解決傷害自己和傷害別人的法寶。
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>實心懺悔是法寶，補救錯誤自己好。我執我見闖大禍，懺其前愆悔後過。
+長期念禮佛大懺悔文，你會在內心有一種制約自己犯錯的力量。這種制約力量，就是以佛菩薩為標準，常生懺悔心，改變自己的過去。懺悔要認識到自己的不足，也要吸取別人的經驗。過去心情難形容，犯錯找理逞英雄。洗心革面像整容，重新做人最光榮
+佛言佛語(十二)</t>
+        </is>
+      </c>
+      <c r="C144" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>